--- a/api/clv1/codelist/SectorCategory.xlsx
+++ b/api/clv1/codelist/SectorCategory.xlsx
@@ -268,7 +268,7 @@
     <t>520</t>
   </si>
   <si>
-    <t>Developmental Food Aid/Food Security Assistance</t>
+    <t>Development Food Assistance</t>
   </si>
   <si>
     <t>530</t>

--- a/api/clv1/codelist/SectorCategory.xlsx
+++ b/api/clv1/codelist/SectorCategory.xlsx
@@ -310,7 +310,7 @@
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>See codes 41050 and 15220 for prevention of floods and conflicts.</t>
+    <t>See code 43060 for disaster risk reduction.</t>
   </si>
   <si>
     <t>910</t>
